--- a/data/b2_indio/B2 Índio 11-2025.xlsx
+++ b/data/b2_indio/B2 Índio 11-2025.xlsx
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>829.1799999999999</v>
+        <v>900.61</v>
       </c>
     </row>
     <row r="3">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>51128.82</v>
+        <v>51243.79</v>
       </c>
     </row>
     <row r="4">
@@ -4779,88 +4779,88 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1453.97</v>
+        <v>3329.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>45970</v>
+        <v>45967</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>2912.8</v>
+        <v>1701.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3900</v>
+        <v>3087.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>45973</v>
+        <v>45971</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1923.79</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>45976</v>
+        <v>45973</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>10425.33</v>
+        <v>2144.23</v>
       </c>
     </row>
     <row r="9">
@@ -4869,70 +4869,70 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1406.66</v>
+        <v>10607.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>45977</v>
+        <v>45976</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>3195.79</v>
+        <v>1576.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>45980</v>
+        <v>45977</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1638.29</v>
+        <v>1359.56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>45981</v>
+        <v>45977</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>18243.91</v>
+        <v>3101.7</v>
       </c>
     </row>
     <row r="13">
@@ -4941,52 +4941,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1651.08</v>
+        <v>18256.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>45983</v>
+        <v>45982</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1243.19</v>
+        <v>2873.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>45984</v>
+        <v>45982</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2220.75</v>
+        <v>1213.05</v>
       </c>
     </row>
     <row r="16">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3477.44</v>
+        <v>3174.49</v>
       </c>
     </row>
     <row r="17">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3032.92</v>
+        <v>2856.12</v>
       </c>
     </row>
   </sheetData>
